--- a/artfynd/A 49015-2022 artfynd.xlsx
+++ b/artfynd/A 49015-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49015-2022 artfynd.xlsx
+++ b/artfynd/A 49015-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96184851</v>
+        <v>96184614</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651685.1425451445</v>
+        <v>651664</v>
       </c>
       <c r="R2" t="n">
-        <v>6645628.683518453</v>
+        <v>6645602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +755,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,24 +775,14 @@
           <t>Blandskog på blockmark</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Högstubbe med barken kvar # Picea abies subsp. abies</t>
+          <t>Horizontal, dead with ground contact # Avbarkad ganska långt nedbruten låga.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,6 +797,409 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96184851</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jälla gymnasium, 1,5 km N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>651685</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6645629</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Högstubbe med barken kvar # Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96182272</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jälla gymnasium, 1,5 km N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>651706</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6645506</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bergssluttning med skogslind, asp och gran.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96182539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jälla gymnasium, 1,5 km N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>651659</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6645591</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog med lindsly och enstaka aspar bland stenblock av olika storlek..</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
